--- a/output/StructureDefinition-DeviceMetric-HiMi.xlsx
+++ b/output/StructureDefinition-DeviceMetric-HiMi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="220">
   <si>
     <t>Property</t>
   </si>
@@ -479,16 +479,23 @@
     <t>Definition of the measurement type</t>
   </si>
   <si>
-    <t xml:space="preserve">Definition of the measurement type of a HiMi device, e.g. that the device only measures tissue glucose. </t>
+    <t>Definition of the measurement type of a HiMi device, e.g. that the device only measures tissue glucose. Only codes from LOINC are allowed. Codes must be match to code in measurements, e.g from this ValueSet. : https://gematik.de/fhir/hdc/ValueSet/VS-Tissue-Glucose-CGM</t>
   </si>
   <si>
     <t>Note: For the OAuth scopes, so that the corresponding FHIR endpoint only returns the allowed device configuration that matches the measurements.</t>
   </si>
   <si>
-    <t>Only codes from LOINC are allowed. Codes must be match to code in measurements, e.g from this ValueSet. : https://gematik.de/fhir/hdc/ValueSet/VS-Tissue-Glucose-CGM</t>
-  </si>
-  <si>
-    <t>http://loinc.org/vs</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Describes the metric type.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/devicemetric-type</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1033,7 +1040,7 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="139.14453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.515625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.9609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
@@ -2292,7 +2299,7 @@
         <v>18</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>18</v>
@@ -2310,10 +2317,10 @@
         <v>106</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>18</v>
@@ -2346,7 +2353,7 @@
         <v>94</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>18</v>
@@ -2354,10 +2361,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2383,13 +2390,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2415,13 +2422,13 @@
         <v>18</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -2439,7 +2446,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2462,10 +2469,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2488,13 +2495,13 @@
         <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2545,7 +2552,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2568,10 +2575,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2594,13 +2601,13 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2651,7 +2658,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2674,10 +2681,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2703,10 +2710,10 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2733,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -2757,7 +2764,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2780,10 +2787,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2809,10 +2816,10 @@
         <v>102</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2839,13 +2846,13 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -2863,7 +2870,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2886,10 +2893,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2915,10 +2922,10 @@
         <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2945,13 +2952,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -2969,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -2984,7 +2991,7 @@
         <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
@@ -2992,10 +2999,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3018,13 +3025,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3075,7 +3082,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -3098,10 +3105,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3124,13 +3131,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3181,7 +3188,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -3204,10 +3211,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3230,13 +3237,13 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3287,7 +3294,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3305,15 +3312,15 @@
         <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3342,7 +3349,7 @@
         <v>129</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>131</v>
@@ -3395,7 +3402,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3413,19 +3420,19 @@
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3447,10 +3454,10 @@
         <v>128</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>131</v>
@@ -3505,7 +3512,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3528,10 +3535,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3557,10 +3564,10 @@
         <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3587,13 +3594,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -3611,7 +3618,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3634,10 +3641,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3663,10 +3670,10 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3693,13 +3700,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -3717,7 +3724,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3740,10 +3747,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3766,13 +3773,13 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3823,7 +3830,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
